--- a/xlxs/New Microsoft Excel Worksheet.xlsx
+++ b/xlxs/New Microsoft Excel Worksheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k\Documents\latex\baocaoktpmud\xlxs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCBE54A-95D3-445E-9F19-433DFB56B32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3E8D81-5415-476D-86E9-6E9887242ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="145">
   <si>
     <t>Quản lý danh mục đơn vị hành chính cấp huyện</t>
   </si>
@@ -187,362 +188,288 @@
     <t>Chức năng tạo các báo cáo thống kê và tổng hợp dữ liệu.</t>
   </si>
   <si>
-    <t>Mã Chức Năng</t>
-  </si>
-  <si>
     <t>Tên Chức Năng</t>
   </si>
   <si>
-    <t>Mô Tả</t>
-  </si>
-  <si>
-    <t>Vai Trò</t>
-  </si>
-  <si>
-    <t>QLND_01</t>
-  </si>
-  <si>
-    <t>Thêm Người Dùng</t>
-  </si>
-  <si>
-    <t>Cho phép Admin thêm người dùng mới vào hệ thống.</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>QLND_02</t>
-  </si>
-  <si>
     <t>Sửa Người Dùng</t>
   </si>
   <si>
-    <t>Cho phép Admin chỉnh sửa thông tin người dùng hiện có.</t>
-  </si>
-  <si>
-    <t>QLND_03</t>
-  </si>
-  <si>
     <t>Xóa Người Dùng</t>
   </si>
   <si>
-    <t>Cho phép Admin xóa người dùng khỏi hệ thống.</t>
-  </si>
-  <si>
-    <t>QLND_04</t>
-  </si>
-  <si>
     <t>Quản Lý Trạng Thái Người Dùng</t>
   </si>
   <si>
-    <t>Quản lý trạng thái hoạt động của người dùng (kích hoạt, vô hiệu hóa).</t>
-  </si>
-  <si>
-    <t>QLND_05</t>
-  </si>
-  <si>
     <t>Quản Lý Nhóm Người Dùng</t>
   </si>
   <si>
-    <t>Tạo và quản lý các nhóm người dùng để dễ dàng phân quyền.</t>
-  </si>
-  <si>
-    <t>QLND_06</t>
-  </si>
-  <si>
     <t>Quản Trị Trạng Thái Nhóm Người Dùng</t>
   </si>
   <si>
-    <t>Quản lý trạng thái hoạt động của nhóm người dùng.</t>
-  </si>
-  <si>
-    <t>QLND_07</t>
-  </si>
-  <si>
-    <t>Tìm Kiếm Người Dùng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm người dùng dựa trên các tiêu chí như tên, email, vai trò.</t>
-  </si>
-  <si>
-    <t>QLND_08</t>
-  </si>
-  <si>
     <t>Tra Cứu Nhóm Người Dùng</t>
   </si>
   <si>
-    <t>Tra cứu thông tin về các nhóm người dùng.</t>
-  </si>
-  <si>
-    <t>QLND_09</t>
-  </si>
-  <si>
     <t>Tra Cứu Phân Quyền Cho Nhóm Người Dùng</t>
   </si>
   <si>
-    <t>Xem và quản lý các quyền hạn được phân bổ cho từng nhóm người dùng.</t>
-  </si>
-  <si>
-    <t>QLND_10</t>
-  </si>
-  <si>
     <t>Tra Cứu Phân Quyền Cho Người Dùng</t>
   </si>
   <si>
-    <t>Xem và quản lý các quyền hạn được phân bổ cho từng người dùng.</t>
-  </si>
-  <si>
-    <t>QLND_11</t>
-  </si>
-  <si>
     <t>Phân Quyền Cho Người Dùng</t>
   </si>
   <si>
-    <t>Gán các quyền hạn cụ thể cho từng người dùng.</t>
-  </si>
-  <si>
-    <t>QLND_12</t>
-  </si>
-  <si>
     <t>Phân Quyền Cho Nhóm Người Dùng</t>
   </si>
   <si>
-    <t>Gán các quyền hạn cụ thể cho nhóm người dùng.</t>
-  </si>
-  <si>
-    <t>TTCB_01</t>
-  </si>
-  <si>
     <t>Đăng Nhập Hệ Thống</t>
   </si>
   <si>
-    <t>Cho phép người dùng đăng nhập vào hệ thống.</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>TTCB_02</t>
-  </si>
-  <si>
     <t>Quên Mật Khẩu</t>
   </si>
   <si>
-    <t>Cho phép người dùng khôi phục mật khẩu khi quên.</t>
-  </si>
-  <si>
-    <t>TTCB_03</t>
-  </si>
-  <si>
     <t>Đổi Mật Khẩu</t>
   </si>
   <si>
-    <t>Cho phép người dùng thay đổi mật khẩu hiện tại.</t>
-  </si>
-  <si>
-    <t>TTCB_04</t>
-  </si>
-  <si>
     <t>Đăng Xuất Khỏi Hệ Thống</t>
   </si>
   <si>
-    <t>Cho phép người dùng đăng xuất khỏi hệ thống một cách an toàn.</t>
-  </si>
-  <si>
-    <t>TTCB_05</t>
-  </si>
-  <si>
     <t>Sửa Thông Tin Tài Khoản</t>
   </si>
   <si>
-    <t>Cho phép người dùng chỉnh sửa thông tin cá nhân.</t>
-  </si>
-  <si>
-    <t>TTCB_06</t>
-  </si>
-  <si>
     <t>Xóa Tài Khoản</t>
   </si>
   <si>
-    <t>Cho phép người dùng xóa tài khoản khỏi hệ thống.</t>
-  </si>
-  <si>
-    <t>QLCB_01</t>
-  </si>
-  <si>
-    <t>Thêm Đơn Vị Hành Chính Cấp Huyện</t>
-  </si>
-  <si>
-    <t>Cho phép quản lý thêm các đơn vị hành chính cấp huyện.</t>
-  </si>
-  <si>
-    <t>Cơ sở</t>
-  </si>
-  <si>
-    <t>QLCB_02</t>
-  </si>
-  <si>
-    <t>Sửa Đơn Vị Hành Chính Cấp Huyện</t>
-  </si>
-  <si>
-    <t>Cho phép chỉnh sửa thông tin đơn vị hành chính cấp huyện.</t>
-  </si>
-  <si>
-    <t>QLCB_03</t>
-  </si>
-  <si>
-    <t>Xóa Đơn Vị Hành Chính Cấp Huyện</t>
-  </si>
-  <si>
-    <t>Cho phép xóa đơn vị hành chính cấp huyện khỏi danh mục.</t>
-  </si>
-  <si>
-    <t>QLCB_04</t>
-  </si>
-  <si>
     <t>Quản Lý Định Nghĩa Quyền</t>
   </si>
   <si>
-    <t>Quản lý các định nghĩa về quyền hạn trong hệ thống.</t>
-  </si>
-  <si>
-    <t>QLCB_05</t>
-  </si>
-  <si>
-    <t>Thêm Đơn Vị Hành Chính Cấp Xã</t>
-  </si>
-  <si>
-    <t>Cho phép quản lý thêm các đơn vị hành chính cấp xã.</t>
-  </si>
-  <si>
-    <t>QLCB_06</t>
-  </si>
-  <si>
-    <t>Sửa Đơn Vị Hành Chính Cấp Xã</t>
-  </si>
-  <si>
-    <t>Cho phép chỉnh sửa thông tin đơn vị hành chính cấp xã.</t>
-  </si>
-  <si>
-    <t>QLCB_07</t>
-  </si>
-  <si>
-    <t>Xóa Đơn Vị Hành Chính Cấp Xã</t>
-  </si>
-  <si>
-    <t>Cho phép xóa đơn vị hành chính cấp xã khỏi danh mục.</t>
-  </si>
-  <si>
-    <t>QLCB_08</t>
-  </si>
-  <si>
-    <t>Tìm Kiếm Danh Mục Đơn Vị Hành Chính Cấp Xã</t>
-  </si>
-  <si>
-    <t>Tìm kiếm các đơn vị hành chính cấp xã dựa trên tiêu chí cụ thể.</t>
-  </si>
-  <si>
-    <t>QLCB_09</t>
-  </si>
-  <si>
-    <t>Tìm Kiếm Đơn Vị Hành Chính Cấp Huyện</t>
-  </si>
-  <si>
-    <t>Tìm kiếm các đơn vị hành chính cấp huyện dựa trên tiêu chí cụ thể.</t>
-  </si>
-  <si>
-    <t>QLLS_01</t>
-  </si>
-  <si>
-    <t>Quản Lý Lịch Sử Truy Cập Người Dùng</t>
-  </si>
-  <si>
-    <t>Theo dõi và quản lý lịch sử truy cập của người dùng.</t>
-  </si>
-  <si>
-    <t>Lịch sử</t>
-  </si>
-  <si>
-    <t>QLLS_02</t>
-  </si>
-  <si>
-    <t>Quản Lý Lịch Sử Tác Động Hệ Thống</t>
-  </si>
-  <si>
-    <t>Theo dõi và quản lý các tác động đến hệ thống (thay đổi cấu hình, cập nhật dữ liệu, v.v.).</t>
-  </si>
-  <si>
-    <t>QLLS_03</t>
-  </si>
-  <si>
-    <t>Tra Cứu Lịch Sử Truy Cập Người Dùng</t>
-  </si>
-  <si>
-    <t>Tra cứu lịch sử truy cập của người dùng cụ thể.</t>
-  </si>
-  <si>
-    <t>QLLS_04</t>
-  </si>
-  <si>
-    <t>Tra Cứu Lịch Sử Tác Động Hệ Thống</t>
-  </si>
-  <si>
-    <t>Tra cứu các tác động đã thực hiện trên hệ thống.</t>
-  </si>
-  <si>
-    <t>BC_01</t>
-  </si>
-  <si>
     <t>Báo Cáo - Thống Kê Người Dùng</t>
   </si>
   <si>
-    <t>Cung cấp báo cáo thống kê về số lượng và phân bố người dùng.</t>
-  </si>
-  <si>
-    <t>Báo cáo</t>
-  </si>
-  <si>
-    <t>BC_02</t>
-  </si>
-  <si>
     <t>Báo Cáo - Thống Kê Lịch Sử Truy Cập Người Dùng</t>
   </si>
   <si>
-    <t>Cung cấp báo cáo về lịch sử truy cập của người dùng.</t>
-  </si>
-  <si>
-    <t>BC_03</t>
-  </si>
-  <si>
     <t>Báo Cáo - Thống Kê Lịch Sử Tác Động Hệ Thống</t>
   </si>
   <si>
-    <t>Cung cấp báo cáo về các tác động đã thực hiện trên hệ thống.</t>
-  </si>
-  <si>
-    <t>BC_04</t>
-  </si>
-  <si>
     <t>Báo Cáo - Thống Kê Tổng Hợp</t>
   </si>
   <si>
-    <t>Cung cấp báo cáo tổng hợp các dữ liệu chính từ hệ thống.</t>
+    <t>Luồng Công Việc</t>
+  </si>
+  <si>
+    <t>truy cập mục báo cáo</t>
+  </si>
+  <si>
+    <t>xem báo cáo</t>
+  </si>
+  <si>
+    <t>truy cập lịch sử tắc động</t>
+  </si>
+  <si>
+    <t>tìm kiếm user</t>
+  </si>
+  <si>
+    <t>ấn tìm kiếm để xem kết quả</t>
+  </si>
+  <si>
+    <t>tìm kiếm người dùng</t>
+  </si>
+  <si>
+    <t>Quản Lý Lịch Sử Truy Cập Người Dùng và lịch sử tắc động hệ thống</t>
+  </si>
+  <si>
+    <t>xem lịch sử tắc động</t>
+  </si>
+  <si>
+    <t>tìm kiếm đơn vị hành chính</t>
+  </si>
+  <si>
+    <t>truy cập danh sách hành chính</t>
+  </si>
+  <si>
+    <t>nhập cơ sở cần tìm kiếm</t>
+  </si>
+  <si>
+    <t>ấn tìm kiếm</t>
+  </si>
+  <si>
+    <t>nhấn phân quyền theo nhóm</t>
+  </si>
+  <si>
+    <t>nhập biểu mẫu</t>
+  </si>
+  <si>
+    <t>Thêm Đơn Vị Hành Chính</t>
+  </si>
+  <si>
+    <t>Sửa Đơn Vị Hành Chính</t>
+  </si>
+  <si>
+    <t>Xóa Đơn Vị Hành Chính</t>
+  </si>
+  <si>
+    <t>tìm kiếm nhóm hành chính</t>
+  </si>
+  <si>
+    <t>chọn cấp hành chính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xem </t>
+  </si>
+  <si>
+    <t>nhập mật khẩu mới</t>
+  </si>
+  <si>
+    <t>xem danh sách người dùng</t>
+  </si>
+  <si>
+    <t>xem nhóm</t>
+  </si>
+  <si>
+    <t>chọn nhóm người dùng có phải admin không phải admin</t>
+  </si>
+  <si>
+    <t>xem trạng thái</t>
+  </si>
+  <si>
+    <t>tên nhóm</t>
+  </si>
+  <si>
+    <t>tên chức năng</t>
+  </si>
+  <si>
+    <t>thêm người dùng</t>
+  </si>
+  <si>
+    <t>tác nhân</t>
+  </si>
+  <si>
+    <t>tiền điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Admin truy cập mục "danh sách người dùng".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Admin truy cập danh sách người dùng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Người dùng truy cập trang đăng nhập.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Người dùng nhấn vào liên kết "Quên mật khẩu".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Người dùng đăng nhập.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Người dùng nhấn nút "Đăng xuất".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Người dùng truy cập mục "Quản lý thông tin tài khoản".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn người dùng cần chỉnh sửa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn người dùng cần xóa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn người dùng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn nhóm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhập cơ sở người dùng dang công tác</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn nhóm để xem các quyền đã được phân.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn người dùng cần phân quyền.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> phân quyền theo nhóm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhập email và mật khẩu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Truy cập mục thông tin tài khoản</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hệ thống kết thúc phiên làm việc và chuyển hướng đến trang đăng nhập.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thay đổi thông tin cần sửa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn "Xóa tài khoản".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Thêm".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn đơn vị cần chỉnh sửa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn đơn vị cần xóa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thay đổi thông tin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Xóa" và xác nhận hành động.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Tìm kiếm" để hiển thị kết quả.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chọn các quyền cần gán.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nhập biểu mẫu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Đăng nhập".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Lưu" để cập nhật.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Xác nhận hành động</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Điền thông tin đơn vị mới.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Cập nhật".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lưu thay đổi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hệ thống xác thực thông tin và chuyển hướng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Lưu" để hoàn tất.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhấn "Cập nhật" để lưu thay đổi.</t>
+  </si>
+  <si>
+    <t>luồng sự kiện chính</t>
+  </si>
+  <si>
+    <t>luồng sự kiện phụ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -560,8 +487,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,8 +515,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -721,72 +672,178 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -797,38 +854,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1146,16 +1178,16 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1163,10 +1195,10 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="14" t="s">
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1174,10 +1206,10 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="15" t="s">
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1185,9 +1217,9 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="16" t="s">
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1196,9 +1228,9 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="9" t="s">
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1206,9 +1238,9 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="10" t="s">
+      <c r="M9" s="43"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1216,11 +1248,11 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="4" t="s">
+      <c r="M10" s="43"/>
+      <c r="N10" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1228,9 +1260,9 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="9" t="s">
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1238,9 +1270,9 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="9" t="s">
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1248,9 +1280,9 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="12" t="s">
+      <c r="M13" s="43"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1258,11 +1290,11 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="4" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1270,9 +1302,9 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="10" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1289,13 +1321,13 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="N17" s="24" t="s">
+      <c r="N17" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="O17" s="20" t="s">
+      <c r="O17" s="12" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1303,16 +1335,16 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="21" t="s">
+      <c r="M18" s="43"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="3:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M19" s="5"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="21" t="s">
+      <c r="M19" s="43"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1320,9 +1352,9 @@
       <c r="C20">
         <v>18</v>
       </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="22" t="s">
+      <c r="M20" s="43"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1330,11 +1362,11 @@
       <c r="C21">
         <v>19</v>
       </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="18" t="s">
+      <c r="M21" s="43"/>
+      <c r="N21" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="O21" s="8" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1342,28 +1374,28 @@
       <c r="C22">
         <v>20</v>
       </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="15" t="s">
+      <c r="M22" s="44"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="3:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="23"/>
+      <c r="O23" s="15"/>
     </row>
     <row r="24" spans="3:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M24" s="4" t="s">
+      <c r="M24" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="O24" s="29" t="s">
+      <c r="O24" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="P24" s="8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1371,10 +1403,10 @@
       <c r="C25">
         <v>21</v>
       </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="14" t="s">
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1382,10 +1414,10 @@
       <c r="C26">
         <v>22</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="15" t="s">
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1393,9 +1425,9 @@
       <c r="C27">
         <v>23</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="32" t="s">
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="18" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1403,95 +1435,95 @@
       <c r="C28">
         <v>24</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="33" t="s">
+      <c r="M28" s="43"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="19" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="3:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M29" s="5"/>
-      <c r="N29" s="4" t="s">
+      <c r="M29" s="43"/>
+      <c r="N29" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="O29" s="33" t="s">
+      <c r="O29" s="19" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="3:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="34" t="s">
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="3:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M32" s="4" t="s">
+      <c r="M32" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="N32" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="O32" s="27" t="s">
+      <c r="O32" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="27" t="s">
+      <c r="M33" s="43"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="34" spans="13:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M34" s="5"/>
-      <c r="N34" s="4" t="s">
+      <c r="M34" s="43"/>
+      <c r="N34" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="O34" s="27" t="s">
+      <c r="O34" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="35" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="27" t="s">
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="36" spans="13:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="13:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M37" s="4" t="s">
+      <c r="M37" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="N37" s="4" t="s">
+      <c r="N37" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="O37" s="27" t="s">
+      <c r="O37" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="38" spans="13:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="27" t="s">
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="39" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="27" t="s">
+      <c r="M39" s="43"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M40" s="6"/>
-      <c r="N40" s="28" t="s">
+      <c r="M40" s="44"/>
+      <c r="N40" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="O40" s="27" t="s">
+      <c r="O40" s="16" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1521,631 +1553,761 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7287BF86-775E-4946-AEB6-EC9095E6A87F}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.5546875" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="54.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
         <v>46</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
+      <c r="D4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="G5" t="s">
+      <c r="D5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" t="s">
+      <c r="D6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="D7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B9" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="B14" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="30"/>
+      <c r="B16" s="31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="B17" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="30"/>
+      <c r="B19" s="31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B20" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="30"/>
+      <c r="B22" s="31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="B23" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="30"/>
+      <c r="B25" s="31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="B26" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="30"/>
+      <c r="B28" s="31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="26" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="B29" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="30"/>
+      <c r="B30" s="31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B31" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="30"/>
+      <c r="B32" s="31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="B33" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="30"/>
+      <c r="B36" s="31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="36" t="s">
+      <c r="B37" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="30"/>
+      <c r="B40" s="31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B43" s="34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="35"/>
+      <c r="B44" s="36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="35"/>
+      <c r="B45" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="37"/>
+      <c r="B46" s="38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="B47" s="34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="35"/>
+      <c r="B48" s="36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="37"/>
+      <c r="B49" s="38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="36" t="s">
+      <c r="B50" s="34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="35"/>
+      <c r="B51" s="36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="35"/>
+      <c r="B52" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="37"/>
+      <c r="B53" s="38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B54" s="34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="37"/>
+      <c r="B55" s="38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="B56" s="34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="35"/>
+      <c r="B57" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="37"/>
+      <c r="B58" s="38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+      <c r="B59" s="34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="35"/>
+      <c r="B60" s="36" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="37"/>
+      <c r="B61" s="38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="28"/>
+      <c r="B65" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="28"/>
+      <c r="B66" s="29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="30"/>
+      <c r="B67" s="31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="28"/>
+      <c r="B69" s="29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="28"/>
+      <c r="B70" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="30"/>
+      <c r="B71" s="31" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="28"/>
+      <c r="B73" s="29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="30"/>
+      <c r="B74" s="31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B75" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="28"/>
+      <c r="B76" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="30"/>
+      <c r="B77" s="31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="28"/>
+      <c r="B79" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="30"/>
+      <c r="B80" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="28"/>
+      <c r="B82" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="30"/>
+      <c r="B83" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="35"/>
+      <c r="B87" s="36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="37"/>
+      <c r="B88" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="37"/>
+      <c r="B90" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="B93" s="27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="28"/>
+      <c r="B94" s="29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="30"/>
+      <c r="B95" s="31"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="36" t="s">
+      <c r="B96" s="27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="30"/>
+      <c r="B97" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B98" s="27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="30"/>
+      <c r="B99" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+      <c r="B100" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="36" t="s">
+    </row>
+    <row r="101" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="30"/>
+      <c r="B101" s="31" t="s">
         <v>77</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44" s="36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="B45" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C45" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" s="36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="B46" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="B47" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="D47" s="36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="B50" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="36" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="C51" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="36" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="D52" s="36" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="B53" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="C53" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34665DF-0479-4DB0-8360-CCCEBB3A2B9F}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="53"/>
+      <c r="B6" s="23">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="53"/>
+      <c r="B7" s="23">
+        <v>2</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="53"/>
+      <c r="B8" s="23">
+        <v>3</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="53"/>
+      <c r="B9" s="24">
+        <v>4</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xlxs/New Microsoft Excel Worksheet.xlsx
+++ b/xlxs/New Microsoft Excel Worksheet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k\Documents\latex\baocaoktpmud\xlxs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3E8D81-5415-476D-86E9-6E9887242ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277D8C85-F176-45AC-9F38-860885444F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="146">
   <si>
     <t>Quản lý danh mục đơn vị hành chính cấp huyện</t>
   </si>
@@ -332,21 +333,6 @@
     <t>xem trạng thái</t>
   </si>
   <si>
-    <t>tên nhóm</t>
-  </si>
-  <si>
-    <t>tên chức năng</t>
-  </si>
-  <si>
-    <t>thêm người dùng</t>
-  </si>
-  <si>
-    <t>tác nhân</t>
-  </si>
-  <si>
-    <t>tiền điều kiện</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Admin truy cập mục "danh sách người dùng".</t>
   </si>
   <si>
@@ -458,10 +444,28 @@
     <t xml:space="preserve"> Nhấn "Cập nhật" để lưu thay đổi.</t>
   </si>
   <si>
-    <t>luồng sự kiện chính</t>
-  </si>
-  <si>
-    <t>luồng sự kiện phụ</t>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Nhóm chức năng</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Cơ sở·</t>
+  </si>
+  <si>
+    <t>User·</t>
+  </si>
+  <si>
+    <t>Lịch sử</t>
+  </si>
+  <si>
+    <t>Báo cáo</t>
+  </si>
+  <si>
+    <t>Tên chức năng</t>
   </si>
 </sst>
 </file>
@@ -740,7 +744,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -812,6 +816,30 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -821,15 +849,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -839,23 +858,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1178,13 +1185,13 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="42" t="s">
+      <c r="N4" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="39" t="s">
+      <c r="O4" s="47" t="s">
         <v>4</v>
       </c>
       <c r="P4" s="8" t="s">
@@ -1195,9 +1202,9 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="40"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="48"/>
       <c r="P5" s="9" t="s">
         <v>38</v>
       </c>
@@ -1206,9 +1213,9 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="49"/>
       <c r="P6" s="10" t="s">
         <v>39</v>
       </c>
@@ -1217,8 +1224,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
       <c r="O7" s="11" t="s">
         <v>6</v>
       </c>
@@ -1228,8 +1235,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
       <c r="O8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1238,8 +1245,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="M9" s="43"/>
-      <c r="N9" s="44"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="40"/>
       <c r="O9" s="5" t="s">
         <v>9</v>
       </c>
@@ -1248,8 +1255,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="M10" s="43"/>
-      <c r="N10" s="42" t="s">
+      <c r="M10" s="41"/>
+      <c r="N10" s="39" t="s">
         <v>41</v>
       </c>
       <c r="O10" s="6" t="s">
@@ -1260,8 +1267,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
       <c r="O11" s="4" t="s">
         <v>10</v>
       </c>
@@ -1270,8 +1277,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
       <c r="O12" s="4" t="s">
         <v>12</v>
       </c>
@@ -1280,8 +1287,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="M13" s="43"/>
-      <c r="N13" s="44"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="40"/>
       <c r="O13" s="7" t="s">
         <v>14</v>
       </c>
@@ -1290,8 +1297,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="42" t="s">
+      <c r="M14" s="41"/>
+      <c r="N14" s="39" t="s">
         <v>42</v>
       </c>
       <c r="O14" s="6" t="s">
@@ -1302,8 +1309,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
       <c r="O15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1321,10 +1328,10 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="M17" s="42" t="s">
+      <c r="M17" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="N17" s="50" t="s">
+      <c r="N17" s="44" t="s">
         <v>43</v>
       </c>
       <c r="O17" s="12" t="s">
@@ -1335,15 +1342,15 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="M18" s="43"/>
-      <c r="N18" s="51"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="45"/>
       <c r="O18" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="3:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M19" s="43"/>
-      <c r="N19" s="51"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="45"/>
       <c r="O19" s="13" t="s">
         <v>27</v>
       </c>
@@ -1352,8 +1359,8 @@
       <c r="C20">
         <v>18</v>
       </c>
-      <c r="M20" s="43"/>
-      <c r="N20" s="52"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="46"/>
       <c r="O20" s="14" t="s">
         <v>28</v>
       </c>
@@ -1362,8 +1369,8 @@
       <c r="C21">
         <v>19</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="48" t="s">
+      <c r="M21" s="41"/>
+      <c r="N21" s="42" t="s">
         <v>26</v>
       </c>
       <c r="O21" s="8" t="s">
@@ -1374,8 +1381,8 @@
       <c r="C22">
         <v>20</v>
       </c>
-      <c r="M22" s="44"/>
-      <c r="N22" s="49"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="43"/>
       <c r="O22" s="10" t="s">
         <v>39</v>
       </c>
@@ -1386,13 +1393,13 @@
       <c r="O23" s="15"/>
     </row>
     <row r="24" spans="3:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M24" s="42" t="s">
+      <c r="M24" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="42" t="s">
+      <c r="N24" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="O24" s="45" t="s">
+      <c r="O24" s="50" t="s">
         <v>0</v>
       </c>
       <c r="P24" s="8" t="s">
@@ -1403,9 +1410,9 @@
       <c r="C25">
         <v>21</v>
       </c>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="46"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="51"/>
       <c r="P25" s="9" t="s">
         <v>38</v>
       </c>
@@ -1414,9 +1421,9 @@
       <c r="C26">
         <v>22</v>
       </c>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="47"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="52"/>
       <c r="P26" s="10" t="s">
         <v>39</v>
       </c>
@@ -1425,8 +1432,8 @@
       <c r="C27">
         <v>23</v>
       </c>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
       <c r="O27" s="18" t="s">
         <v>7</v>
       </c>
@@ -1435,15 +1442,15 @@
       <c r="C28">
         <v>24</v>
       </c>
-      <c r="M28" s="43"/>
-      <c r="N28" s="44"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="40"/>
       <c r="O28" s="19" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="3:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M29" s="43"/>
-      <c r="N29" s="42" t="s">
+      <c r="M29" s="41"/>
+      <c r="N29" s="39" t="s">
         <v>41</v>
       </c>
       <c r="O29" s="19" t="s">
@@ -1451,18 +1458,18 @@
       </c>
     </row>
     <row r="30" spans="3:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
       <c r="O30" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="3:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M32" s="42" t="s">
+      <c r="M32" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="N32" s="42" t="s">
+      <c r="N32" s="39" t="s">
         <v>40</v>
       </c>
       <c r="O32" s="16" t="s">
@@ -1470,15 +1477,15 @@
       </c>
     </row>
     <row r="33" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M33" s="43"/>
-      <c r="N33" s="44"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="40"/>
       <c r="O33" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="34" spans="13:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M34" s="43"/>
-      <c r="N34" s="42" t="s">
+      <c r="M34" s="41"/>
+      <c r="N34" s="39" t="s">
         <v>41</v>
       </c>
       <c r="O34" s="16" t="s">
@@ -1486,18 +1493,18 @@
       </c>
     </row>
     <row r="35" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M35" s="44"/>
-      <c r="N35" s="44"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
       <c r="O35" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="36" spans="13:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="13:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M37" s="42" t="s">
+      <c r="M37" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="N37" s="42" t="s">
+      <c r="N37" s="39" t="s">
         <v>36</v>
       </c>
       <c r="O37" s="16" t="s">
@@ -1505,21 +1512,21 @@
       </c>
     </row>
     <row r="38" spans="13:15" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
       <c r="O38" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="39" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M39" s="43"/>
-      <c r="N39" s="44"/>
+      <c r="M39" s="41"/>
+      <c r="N39" s="40"/>
       <c r="O39" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="13:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M40" s="44"/>
+      <c r="M40" s="40"/>
       <c r="N40" s="17" t="s">
         <v>44</v>
       </c>
@@ -1529,6 +1536,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="O4:O6"/>
+    <mergeCell ref="M4:M15"/>
+    <mergeCell ref="M17:M22"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="M24:M30"/>
     <mergeCell ref="N32:N33"/>
     <mergeCell ref="N37:N39"/>
     <mergeCell ref="M32:M35"/>
@@ -1541,11 +1553,6 @@
     <mergeCell ref="N24:N28"/>
     <mergeCell ref="N29:N30"/>
     <mergeCell ref="N34:N35"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="M4:M15"/>
-    <mergeCell ref="M17:M22"/>
-    <mergeCell ref="O24:O26"/>
-    <mergeCell ref="M24:M30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1553,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7287BF86-775E-4946-AEB6-EC9095E6A87F}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.5546875" customWidth="1"/>
@@ -1562,12 +1569,12 @@
     <col min="4" max="4" width="54.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>46</v>
       </c>
@@ -1575,7 +1582,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>32</v>
       </c>
@@ -1583,7 +1590,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>33</v>
       </c>
@@ -1591,7 +1598,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>34</v>
       </c>
@@ -1599,7 +1606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>35</v>
       </c>
@@ -1607,7 +1614,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>36</v>
       </c>
@@ -1615,221 +1622,310 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>53</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="28"/>
       <c r="B11" s="29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="30"/>
       <c r="B13" s="31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
         <v>55</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="30"/>
       <c r="B16" s="31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
         <v>56</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="28"/>
       <c r="B18" s="29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="30"/>
       <c r="B19" s="31" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
         <v>57</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="28"/>
       <c r="B21" s="29" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="30"/>
       <c r="B22" s="31" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="E23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="30"/>
       <c r="B25" s="31" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>59</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="E26">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
       <c r="B27" s="29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="E27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="30"/>
       <c r="B28" s="31" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="E28">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+      <c r="E29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="30"/>
       <c r="B30" s="31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="E30">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
         <v>61</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+      <c r="E31">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="30"/>
       <c r="B32" s="31" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="26" t="s">
         <v>62</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="E33">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="28"/>
       <c r="B34" s="29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="E34">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="28"/>
       <c r="B35" s="29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+      <c r="E35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="30"/>
       <c r="B36" s="31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="E36">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="26" t="s">
         <v>63</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="28"/>
       <c r="B39" s="29" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="30"/>
       <c r="B40" s="31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="32" t="s">
         <v>53</v>
       </c>
@@ -1837,41 +1933,41 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>64</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="35"/>
       <c r="B44" s="36" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="35"/>
       <c r="B45" s="36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="37"/>
       <c r="B46" s="38" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="35"/>
       <c r="B48" s="36" t="s">
         <v>89</v>
@@ -1880,7 +1976,7 @@
     <row r="49" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="37"/>
       <c r="B49" s="38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1888,13 +1984,13 @@
         <v>66</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="35"/>
       <c r="B51" s="36" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1906,7 +2002,7 @@
     <row r="53" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="37"/>
       <c r="B53" s="38" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1914,13 +2010,13 @@
         <v>67</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="37"/>
       <c r="B55" s="38" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1928,19 +2024,19 @@
         <v>68</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="35"/>
       <c r="B57" s="36" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="37"/>
       <c r="B58" s="38" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1948,19 +2044,19 @@
         <v>69</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="35"/>
       <c r="B60" s="36" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="37"/>
       <c r="B61" s="38" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1982,19 +2078,19 @@
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="28"/>
       <c r="B65" s="29" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="28"/>
       <c r="B66" s="29" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="30"/>
       <c r="B67" s="31" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -2008,19 +2104,19 @@
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="28"/>
       <c r="B69" s="29" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="28"/>
       <c r="B70" s="29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="30"/>
       <c r="B71" s="31" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -2034,13 +2130,13 @@
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="28"/>
       <c r="B73" s="29" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="30"/>
       <c r="B74" s="31" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -2215,12 +2311,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34665DF-0479-4DB0-8360-CCCEBB3A2B9F}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A4:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2228,81 +2325,31 @@
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>105</v>
-      </c>
-    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="A5" s="53"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="53"/>
-      <c r="B6" s="23">
-        <v>1</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>106</v>
-      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="27"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="53"/>
-      <c r="B7" s="23">
-        <v>2</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>113</v>
-      </c>
+      <c r="B7" s="23"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="53"/>
-      <c r="B8" s="23">
-        <v>3</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>129</v>
-      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="29"/>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="53"/>
-      <c r="B9" s="24">
-        <v>4</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>144</v>
-      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2310,4 +2357,351 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16D40E2-491F-428B-95EE-ECEB306D07E1}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="54"/>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="54"/>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="54"/>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="54"/>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="54"/>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="54"/>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" s="54"/>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" s="54"/>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" s="54"/>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" s="54"/>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" s="54"/>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" s="54"/>
+      <c r="C21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" s="54"/>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" s="54"/>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" s="54"/>
+      <c r="C24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="54"/>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" s="54"/>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" s="54"/>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" s="54"/>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" s="54"/>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B31:B34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>